--- a/Encuestas de Satisfacción/Facilitador ev. por el Supervisor/Supervisor al Facilitador.xlsx
+++ b/Encuestas de Satisfacción/Facilitador ev. por el Supervisor/Supervisor al Facilitador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Benjo\Prácticas Laborales I\Reportes Automáticos\encuestas_app\Encuestas de Satisfacción\Facilitador ev. por el Supervisor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C64E15-1C44-468F-BCAC-B1FE7F305245}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28AC8E4-B14A-4E69-9DEA-AF64973C5CDD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{14A46E89-9908-44B2-BA80-90675873EFB7}"/>
   </bookViews>
@@ -48,15 +48,9 @@
     <t>FECHA FIN: Friday, 3 de July de 2026, 23:55</t>
   </si>
   <si>
-    <t>RESPUESTAS ENVIADAS: 140</t>
-  </si>
-  <si>
     <t>Wednesday, 3 de June de 2026, 15:22</t>
   </si>
   <si>
-    <t>Preguntas: 19</t>
-  </si>
-  <si>
     <t>Etiqueta</t>
   </si>
   <si>
@@ -127,6 +121,12 @@
   </si>
   <si>
     <t>No Si</t>
+  </si>
+  <si>
+    <t>RESPUESTAS ENVIADAS: 1</t>
+  </si>
+  <si>
+    <t>Preguntas: 12</t>
   </si>
 </sst>
 </file>
@@ -510,7 +510,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -550,61 +550,66 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="J14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
@@ -628,7 +633,7 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4">
         <v>0</v>
@@ -652,7 +657,7 @@
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C17" s="4">
         <v>0</v>
@@ -676,7 +681,7 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
@@ -700,7 +705,7 @@
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" s="4">
         <v>1</v>
@@ -724,7 +729,7 @@
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
@@ -748,7 +753,7 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C21" s="4">
         <v>1</v>
@@ -772,7 +777,7 @@
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4">
         <v>0</v>
@@ -796,7 +801,7 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C23" s="4">
         <v>1</v>
@@ -820,7 +825,7 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" s="4">
         <v>0</v>
@@ -844,7 +849,7 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C25" s="4">
         <v>0</v>
@@ -868,10 +873,10 @@
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="4"/>
@@ -883,7 +888,7 @@
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
@@ -895,7 +900,7 @@
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="4"/>
